--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/55.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/55.xlsx
@@ -426,13 +426,13 @@
         <v>-9.602850342331335</v>
       </c>
       <c r="E2">
-        <v>-23.48178364254319</v>
+        <v>-24.73840348035366</v>
       </c>
       <c r="F2">
-        <v>-4.546396061791661</v>
+        <v>-3.872096712238835</v>
       </c>
       <c r="G2">
-        <v>-12.8627186464052</v>
+        <v>-12.61129926542525</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.424407765267254</v>
       </c>
       <c r="E3">
-        <v>-21.92935935407768</v>
+        <v>-26.1545252296623</v>
       </c>
       <c r="F3">
-        <v>-4.154389412499657</v>
+        <v>-3.446498108028506</v>
       </c>
       <c r="G3">
-        <v>-12.51074475521543</v>
+        <v>-13.01493421975535</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.190381285178798</v>
       </c>
       <c r="E4">
-        <v>-25.29872062627073</v>
+        <v>-26.03324363878887</v>
       </c>
       <c r="F4">
-        <v>-4.320579794318904</v>
+        <v>-2.982602422051949</v>
       </c>
       <c r="G4">
-        <v>-13.64029296157814</v>
+        <v>-12.68676315099294</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.913128498722449</v>
       </c>
       <c r="E5">
-        <v>-24.38907246692796</v>
+        <v>-26.02658678199759</v>
       </c>
       <c r="F5">
-        <v>-3.917362020597412</v>
+        <v>-3.645504264509656</v>
       </c>
       <c r="G5">
-        <v>-13.62119773490762</v>
+        <v>-13.38479829903935</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.600653401775359</v>
       </c>
       <c r="E6">
-        <v>-23.85099012838855</v>
+        <v>-24.68037561441937</v>
       </c>
       <c r="F6">
-        <v>-4.727375286853089</v>
+        <v>-3.554332491422737</v>
       </c>
       <c r="G6">
-        <v>-11.16584556152313</v>
+        <v>-14.00453076871814</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.263516277819431</v>
       </c>
       <c r="E7">
-        <v>-24.39739127368005</v>
+        <v>-25.52768480057255</v>
       </c>
       <c r="F7">
-        <v>-4.170631212166347</v>
+        <v>-3.104635022730164</v>
       </c>
       <c r="G7">
-        <v>-12.67162733678739</v>
+        <v>-15.27908749079201</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.907349229914336</v>
       </c>
       <c r="E8">
-        <v>-24.42083065514375</v>
+        <v>-24.90424072698856</v>
       </c>
       <c r="F8">
-        <v>-3.518284427155111</v>
+        <v>-3.167132858169178</v>
       </c>
       <c r="G8">
-        <v>-13.04053466841053</v>
+        <v>-14.16854347109748</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.539328348460238</v>
       </c>
       <c r="E9">
-        <v>-26.46554988145711</v>
+        <v>-27.5771226968019</v>
       </c>
       <c r="F9">
-        <v>-3.44082710478894</v>
+        <v>-2.456033286746985</v>
       </c>
       <c r="G9">
-        <v>-13.36135963662131</v>
+        <v>-12.1271121170336</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.166031849962218</v>
       </c>
       <c r="E10">
-        <v>-24.88934657597733</v>
+        <v>-26.42059571998297</v>
       </c>
       <c r="F10">
-        <v>-3.445059233849843</v>
+        <v>-3.1459531604144</v>
       </c>
       <c r="G10">
-        <v>-13.48726961511641</v>
+        <v>-13.20854154398301</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.792848949098783</v>
       </c>
       <c r="E11">
-        <v>-25.8943462840256</v>
+        <v>-27.06116648226397</v>
       </c>
       <c r="F11">
-        <v>-3.326328505639187</v>
+        <v>-3.010885370285732</v>
       </c>
       <c r="G11">
-        <v>-12.34569750735506</v>
+        <v>-12.78629139208559</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.424097029246104</v>
       </c>
       <c r="E12">
-        <v>-25.77970343604742</v>
+        <v>-27.36513124308083</v>
       </c>
       <c r="F12">
-        <v>-3.424533946343277</v>
+        <v>-2.207505670191674</v>
       </c>
       <c r="G12">
-        <v>-12.73253144307336</v>
+        <v>-13.11198617278463</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.061008222873233</v>
       </c>
       <c r="E13">
-        <v>-27.14761052259639</v>
+        <v>-28.70906458823319</v>
       </c>
       <c r="F13">
-        <v>-2.761220405286378</v>
+        <v>-1.86004364961781</v>
       </c>
       <c r="G13">
-        <v>-12.72397699339989</v>
+        <v>-12.39528616898781</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.711342957371637</v>
       </c>
       <c r="E14">
-        <v>-24.72577356634627</v>
+        <v>-27.52780308638436</v>
       </c>
       <c r="F14">
-        <v>-2.581446454796024</v>
+        <v>-1.786616334666259</v>
       </c>
       <c r="G14">
-        <v>-10.46469187957872</v>
+        <v>-12.89860827059644</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.378284015260389</v>
       </c>
       <c r="E15">
-        <v>-26.74541410360515</v>
+        <v>-28.81945972759218</v>
       </c>
       <c r="F15">
-        <v>-3.043006973064089</v>
+        <v>-2.465446025544995</v>
       </c>
       <c r="G15">
-        <v>-11.58700323339259</v>
+        <v>-12.26466859473586</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.063380625051439</v>
       </c>
       <c r="E16">
-        <v>-27.52843707274544</v>
+        <v>-29.52943161827773</v>
       </c>
       <c r="F16">
-        <v>-2.507983520046153</v>
+        <v>-1.274845983012308</v>
       </c>
       <c r="G16">
-        <v>-12.83086457722633</v>
+        <v>-11.82303850925154</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.769435725427853</v>
       </c>
       <c r="E17">
-        <v>-29.39345286501241</v>
+        <v>-31.45154241083342</v>
       </c>
       <c r="F17">
-        <v>-2.716698970855516</v>
+        <v>-1.379262522502588</v>
       </c>
       <c r="G17">
-        <v>-11.11522732022767</v>
+        <v>-12.22517709699789</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.499334831734658</v>
       </c>
       <c r="E18">
-        <v>-27.91909041149113</v>
+        <v>-31.23860224180774</v>
       </c>
       <c r="F18">
-        <v>-3.346070985950107</v>
+        <v>-1.667974241767703</v>
       </c>
       <c r="G18">
-        <v>-10.92221589419708</v>
+        <v>-11.38998604725948</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.256146000889777</v>
       </c>
       <c r="E19">
-        <v>-28.95017865829759</v>
+        <v>-29.02639287584668</v>
       </c>
       <c r="F19">
-        <v>-2.267139011151807</v>
+        <v>-1.140567627018508</v>
       </c>
       <c r="G19">
-        <v>-10.74852812247922</v>
+        <v>-11.19736195505699</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.043256584935479</v>
       </c>
       <c r="E20">
-        <v>-30.1340870532039</v>
+        <v>-28.35918562945256</v>
       </c>
       <c r="F20">
-        <v>-2.59758636527217</v>
+        <v>-1.564964270127376</v>
       </c>
       <c r="G20">
-        <v>-10.50719597375743</v>
+        <v>-11.81500712577327</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.864551606435826</v>
       </c>
       <c r="E21">
-        <v>-29.21829149039572</v>
+        <v>-31.96526155921156</v>
       </c>
       <c r="F21">
-        <v>-2.131808628556452</v>
+        <v>-0.9752760238312973</v>
       </c>
       <c r="G21">
-        <v>-10.8377241509438</v>
+        <v>-10.85680613543216</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.728001541759012</v>
       </c>
       <c r="E22">
-        <v>-28.41439225608007</v>
+        <v>-29.63078339504341</v>
       </c>
       <c r="F22">
-        <v>-1.90377730664861</v>
+        <v>-0.6563868800821968</v>
       </c>
       <c r="G22">
-        <v>-10.05616393894158</v>
+        <v>-11.01352405071572</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.638634222381852</v>
       </c>
       <c r="E23">
-        <v>-28.98219496953182</v>
+        <v>-32.48116343206139</v>
       </c>
       <c r="F23">
-        <v>-2.135074881225691</v>
+        <v>-1.424404404118147</v>
       </c>
       <c r="G23">
-        <v>-9.731346452810449</v>
+        <v>-10.66138463224898</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.598823293277485</v>
       </c>
       <c r="E24">
-        <v>-30.16777663558397</v>
+        <v>-30.98360613467282</v>
       </c>
       <c r="F24">
-        <v>-1.647732255912894</v>
+        <v>-0.8087037646393587</v>
       </c>
       <c r="G24">
-        <v>-10.43246702929946</v>
+        <v>-9.891523888182546</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.613528025407187</v>
       </c>
       <c r="E25">
-        <v>-28.58801394953415</v>
+        <v>-31.28043628469059</v>
       </c>
       <c r="F25">
-        <v>-2.180668223075775</v>
+        <v>-1.507058903569482</v>
       </c>
       <c r="G25">
-        <v>-10.05987837103664</v>
+        <v>-10.87440499551893</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.685164012902977</v>
       </c>
       <c r="E26">
-        <v>-29.32172183673091</v>
+        <v>-29.76630477243395</v>
       </c>
       <c r="F26">
-        <v>-1.732540510611507</v>
+        <v>-1.471565017094329</v>
       </c>
       <c r="G26">
-        <v>-9.834549399451689</v>
+        <v>-11.61526205011581</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.81397872783845</v>
       </c>
       <c r="E27">
-        <v>-28.2903075397959</v>
+        <v>-30.20857818639308</v>
       </c>
       <c r="F27">
-        <v>-2.433946526686141</v>
+        <v>-1.586042907059012</v>
       </c>
       <c r="G27">
-        <v>-9.905431489993024</v>
+        <v>-10.99577952662523</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.997055226734468</v>
       </c>
       <c r="E28">
-        <v>-29.24257316802485</v>
+        <v>-30.65605934546102</v>
       </c>
       <c r="F28">
-        <v>-2.4892673869473</v>
+        <v>-1.533140879614027</v>
       </c>
       <c r="G28">
-        <v>-9.356288127575338</v>
+        <v>-10.3729632837766</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.23026043493801</v>
       </c>
       <c r="E29">
-        <v>-28.75214396146816</v>
+        <v>-29.58779685552559</v>
       </c>
       <c r="F29">
-        <v>-2.02549181424415</v>
+        <v>-0.8464176757540146</v>
       </c>
       <c r="G29">
-        <v>-10.80141739801461</v>
+        <v>-11.79755724023578</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.507522700876488</v>
       </c>
       <c r="E30">
-        <v>-27.53754836244887</v>
+        <v>-31.45249339037503</v>
       </c>
       <c r="F30">
-        <v>-1.984548926993381</v>
+        <v>-1.007769563573511</v>
       </c>
       <c r="G30">
-        <v>-10.66505271670649</v>
+        <v>-11.62212481101872</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.819287273127431</v>
       </c>
       <c r="E31">
-        <v>-27.03787654044252</v>
+        <v>-29.32508649291861</v>
       </c>
       <c r="F31">
-        <v>-1.932495976136266</v>
+        <v>-1.238925487324713</v>
       </c>
       <c r="G31">
-        <v>-10.48286677458932</v>
+        <v>-12.68513436258762</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.152415400167957</v>
       </c>
       <c r="E32">
-        <v>-26.7763843373436</v>
+        <v>-30.86347704043435</v>
       </c>
       <c r="F32">
-        <v>-2.206301223988004</v>
+        <v>-1.70651403518295</v>
       </c>
       <c r="G32">
-        <v>-11.09878384053411</v>
+        <v>-11.64752662694154</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.498034219968138</v>
       </c>
       <c r="E33">
-        <v>-27.82967116373567</v>
+        <v>-29.97905474555131</v>
       </c>
       <c r="F33">
-        <v>-1.774605835693069</v>
+        <v>-1.518494515565129</v>
       </c>
       <c r="G33">
-        <v>-10.75020987961317</v>
+        <v>-10.34794880168186</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.844968604053462</v>
       </c>
       <c r="E34">
-        <v>-26.99795804206491</v>
+        <v>-27.76004587586774</v>
       </c>
       <c r="F34">
-        <v>-1.964126357044762</v>
+        <v>-2.086520125910598</v>
       </c>
       <c r="G34">
-        <v>-11.39723945253602</v>
+        <v>-11.31828956251548</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.182307759845002</v>
       </c>
       <c r="E35">
-        <v>-24.28065174223632</v>
+        <v>-27.95197618973483</v>
       </c>
       <c r="F35">
-        <v>-2.109141182946247</v>
+        <v>-2.052810542821075</v>
       </c>
       <c r="G35">
-        <v>-11.88558795667054</v>
+        <v>-11.68846814362571</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.498898420906196</v>
       </c>
       <c r="E36">
-        <v>-26.23638645429895</v>
+        <v>-27.77168405406745</v>
       </c>
       <c r="F36">
-        <v>-2.025188631774725</v>
+        <v>-1.033270025701291</v>
       </c>
       <c r="G36">
-        <v>-11.66651922670034</v>
+        <v>-12.31664084915688</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.785979798488541</v>
       </c>
       <c r="E37">
-        <v>-25.72561987097381</v>
+        <v>-27.49471352681032</v>
       </c>
       <c r="F37">
-        <v>-1.857616533127608</v>
+        <v>-1.384754598383149</v>
       </c>
       <c r="G37">
-        <v>-11.44889058403973</v>
+        <v>-11.8877596745443</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.036028027979532</v>
       </c>
       <c r="E38">
-        <v>-25.7366512336565</v>
+        <v>-28.0889263006748</v>
       </c>
       <c r="F38">
-        <v>-1.898177543005685</v>
+        <v>-1.204250027843526</v>
       </c>
       <c r="G38">
-        <v>-11.19218757237911</v>
+        <v>-12.3577809985734</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.241448325040226</v>
       </c>
       <c r="E39">
-        <v>-24.52186543872889</v>
+        <v>-26.33148440846003</v>
       </c>
       <c r="F39">
-        <v>-2.1472982706214</v>
+        <v>-0.5577655989419017</v>
       </c>
       <c r="G39">
-        <v>-12.05346903151252</v>
+        <v>-11.74192683299386</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.396620719538651</v>
       </c>
       <c r="E40">
-        <v>-25.51226987505044</v>
+        <v>-27.2854708568119</v>
       </c>
       <c r="F40">
-        <v>-1.996291863295467</v>
+        <v>-1.088186642669884</v>
       </c>
       <c r="G40">
-        <v>-11.69755890167655</v>
+        <v>-12.01558976945218</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.501349421766498</v>
       </c>
       <c r="E41">
-        <v>-23.63201576774765</v>
+        <v>-25.79862792892547</v>
       </c>
       <c r="F41">
-        <v>-1.704032246444162</v>
+        <v>-1.67372559664534</v>
       </c>
       <c r="G41">
-        <v>-10.52309321343701</v>
+        <v>-13.32767814630476</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.557097982770709</v>
       </c>
       <c r="E42">
-        <v>-25.38372461186871</v>
+        <v>-26.73649300981004</v>
       </c>
       <c r="F42">
-        <v>-1.244871508542008</v>
+        <v>-1.805790554938859</v>
       </c>
       <c r="G42">
-        <v>-11.31564774717515</v>
+        <v>-10.28232385745689</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.568176460488833</v>
       </c>
       <c r="E43">
-        <v>-24.3370810568459</v>
+        <v>-27.58576755368254</v>
       </c>
       <c r="F43">
-        <v>-1.76820586913904</v>
+        <v>-1.009273050409592</v>
       </c>
       <c r="G43">
-        <v>-11.77746553935794</v>
+        <v>-10.03651585116601</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.539858582662669</v>
       </c>
       <c r="E44">
-        <v>-24.46380587347655</v>
+        <v>-24.37942228881762</v>
       </c>
       <c r="F44">
-        <v>-1.963593716804762</v>
+        <v>-1.940958577523266</v>
       </c>
       <c r="G44">
-        <v>-10.45438284076943</v>
+        <v>-11.43298341272354</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.483486529139015</v>
       </c>
       <c r="E45">
-        <v>-22.79991319731223</v>
+        <v>-24.20814634489951</v>
       </c>
       <c r="F45">
-        <v>-2.134984589178786</v>
+        <v>-1.018955836980915</v>
       </c>
       <c r="G45">
-        <v>-11.09698952485182</v>
+        <v>-11.33772577537655</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.409480918395662</v>
       </c>
       <c r="E46">
-        <v>-23.06539498601191</v>
+        <v>-27.7561876160132</v>
       </c>
       <c r="F46">
-        <v>-1.700826464595328</v>
+        <v>-1.260666818178588</v>
       </c>
       <c r="G46">
-        <v>-11.25714047585961</v>
+        <v>-12.12738358176782</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.326941555534234</v>
       </c>
       <c r="E47">
-        <v>-21.08538765326816</v>
+        <v>-25.792442033431</v>
       </c>
       <c r="F47">
-        <v>-1.953442074283454</v>
+        <v>-0.6554400561407969</v>
       </c>
       <c r="G47">
-        <v>-10.30147867394711</v>
+        <v>-11.12097111673831</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.246807379823093</v>
       </c>
       <c r="E48">
-        <v>-22.84345900336999</v>
+        <v>-24.66400970935565</v>
       </c>
       <c r="F48">
-        <v>-1.690194368980397</v>
+        <v>-1.220315385253419</v>
       </c>
       <c r="G48">
-        <v>-9.165848995428762</v>
+        <v>-12.01565598036296</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.180331460746697</v>
       </c>
       <c r="E49">
-        <v>-20.97493817222108</v>
+        <v>-23.69089951526939</v>
       </c>
       <c r="F49">
-        <v>-2.41675458960844</v>
+        <v>-1.405364379364801</v>
       </c>
       <c r="G49">
-        <v>-10.96811660809908</v>
+        <v>-11.43845905504549</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.13659512597668</v>
       </c>
       <c r="E50">
-        <v>-22.00892917086646</v>
+        <v>-23.87380005196519</v>
       </c>
       <c r="F50">
-        <v>-2.468471223300019</v>
+        <v>-1.48859128069147</v>
       </c>
       <c r="G50">
-        <v>-10.5737909078254</v>
+        <v>-10.07753682094312</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.122310658915465</v>
       </c>
       <c r="E51">
-        <v>-19.53950700974374</v>
+        <v>-24.20233631274766</v>
       </c>
       <c r="F51">
-        <v>-2.586093595925729</v>
+        <v>-1.106552376357352</v>
       </c>
       <c r="G51">
-        <v>-9.114429602112802</v>
+        <v>-11.6940397917683</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.141020196418552</v>
       </c>
       <c r="E52">
-        <v>-21.64299224325463</v>
+        <v>-23.46353389229228</v>
       </c>
       <c r="F52">
-        <v>-2.550328833309861</v>
+        <v>-1.619799707090495</v>
       </c>
       <c r="G52">
-        <v>-10.85829588092483</v>
+        <v>-11.51688587887083</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.197856994576973</v>
       </c>
       <c r="E53">
-        <v>-20.82044022450139</v>
+        <v>-23.28146206633988</v>
       </c>
       <c r="F53">
-        <v>-2.855959956777155</v>
+        <v>-1.745215360241743</v>
       </c>
       <c r="G53">
-        <v>-11.48391284529968</v>
+        <v>-12.30564321687542</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.292919721447043</v>
       </c>
       <c r="E54">
-        <v>-20.25990118335795</v>
+        <v>-23.4489657914096</v>
       </c>
       <c r="F54">
-        <v>-2.777260911674188</v>
+        <v>-0.5779877039790432</v>
       </c>
       <c r="G54">
-        <v>-10.38472234153209</v>
+        <v>-10.85553819649062</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.420245878148156</v>
       </c>
       <c r="E55">
-        <v>-20.79247236903002</v>
+        <v>-24.94083532544454</v>
       </c>
       <c r="F55">
-        <v>-2.532692891304259</v>
+        <v>-1.350169430948867</v>
       </c>
       <c r="G55">
-        <v>-10.93902022335442</v>
+        <v>-11.94618087167582</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.576698786345429</v>
       </c>
       <c r="E56">
-        <v>-20.32248922261796</v>
+        <v>-22.77344879521141</v>
       </c>
       <c r="F56">
-        <v>-3.102123412764875</v>
+        <v>-0.9134276284360778</v>
       </c>
       <c r="G56">
-        <v>-11.45023797607422</v>
+        <v>-12.04737762772026</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.756123914831163</v>
       </c>
       <c r="E57">
-        <v>-19.85213474133727</v>
+        <v>-22.76999809801756</v>
       </c>
       <c r="F57">
-        <v>-2.942622926090636</v>
+        <v>-1.608620888989715</v>
       </c>
       <c r="G57">
-        <v>-11.51903442292581</v>
+        <v>-11.28221454777405</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.95052932007273</v>
       </c>
       <c r="E58">
-        <v>-21.1093795085608</v>
+        <v>-21.78163600347347</v>
       </c>
       <c r="F58">
-        <v>-2.661682121431184</v>
+        <v>-0.8856574396246272</v>
       </c>
       <c r="G58">
-        <v>-11.91897149788855</v>
+        <v>-10.92622827539068</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.150342202321683</v>
       </c>
       <c r="E59">
-        <v>-20.37904986297376</v>
+        <v>-22.92091855127119</v>
       </c>
       <c r="F59">
-        <v>-2.96017354625375</v>
+        <v>-1.690369154502387</v>
       </c>
       <c r="G59">
-        <v>-9.731164372805789</v>
+        <v>-11.30512683345134</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.346553644563977</v>
       </c>
       <c r="E60">
-        <v>-19.26198853713167</v>
+        <v>-22.60000824071763</v>
       </c>
       <c r="F60">
-        <v>-2.799472755212854</v>
+        <v>-1.344719601805849</v>
       </c>
       <c r="G60">
-        <v>-9.298870025742218</v>
+        <v>-12.12445374896557</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.532251544069529</v>
       </c>
       <c r="E61">
-        <v>-20.9697575979563</v>
+        <v>-22.11180251489871</v>
       </c>
       <c r="F61">
-        <v>-3.077525871106147</v>
+        <v>-1.860683977620174</v>
       </c>
       <c r="G61">
-        <v>-11.69646973219413</v>
+        <v>-11.6875147065104</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.699124656783411</v>
       </c>
       <c r="E62">
-        <v>-21.07690129297778</v>
+        <v>-22.01453542168796</v>
       </c>
       <c r="F62">
-        <v>-3.056450547644122</v>
+        <v>-1.897058418644503</v>
       </c>
       <c r="G62">
-        <v>-11.31828625196995</v>
+        <v>-11.60508212258255</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.837221310555622</v>
       </c>
       <c r="E63">
-        <v>-20.5748429651694</v>
+        <v>-23.22040012282046</v>
       </c>
       <c r="F63">
-        <v>-3.109359202028329</v>
+        <v>-1.725507671361739</v>
       </c>
       <c r="G63">
-        <v>-10.71405872232433</v>
+        <v>-11.35449368853295</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.944680474780361</v>
       </c>
       <c r="E64">
-        <v>-20.92661029761122</v>
+        <v>-22.27449700057228</v>
       </c>
       <c r="F64">
-        <v>-2.806476601603523</v>
+        <v>-1.911365980425656</v>
       </c>
       <c r="G64">
-        <v>-10.32273899740031</v>
+        <v>-11.59387923647765</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.019069970957268</v>
       </c>
       <c r="E65">
-        <v>-20.79229575854372</v>
+        <v>-21.60184652842094</v>
       </c>
       <c r="F65">
-        <v>-3.077228487208542</v>
+        <v>-2.076752845864189</v>
       </c>
       <c r="G65">
-        <v>-11.2988003809258</v>
+        <v>-11.39347867280341</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.060464043795372</v>
       </c>
       <c r="E66">
-        <v>-20.65428145621195</v>
+        <v>-23.34406821949593</v>
       </c>
       <c r="F66">
-        <v>-2.944297884979097</v>
+        <v>-1.881202638187518</v>
       </c>
       <c r="G66">
-        <v>-10.94728665556598</v>
+        <v>-12.04557669094689</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.069434860191047</v>
       </c>
       <c r="E67">
-        <v>-20.07551983566164</v>
+        <v>-24.68599545066289</v>
       </c>
       <c r="F67">
-        <v>-3.281898191622633</v>
+        <v>-2.115366363978285</v>
       </c>
       <c r="G67">
-        <v>-11.14509175153743</v>
+        <v>-12.47977791224108</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.0511863326292</v>
       </c>
       <c r="E68">
-        <v>-20.08018416388954</v>
+        <v>-22.37544121467726</v>
       </c>
       <c r="F68">
-        <v>-2.711314582737319</v>
+        <v>-1.772649231887657</v>
       </c>
       <c r="G68">
-        <v>-9.771907256757599</v>
+        <v>-11.94786262880977</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.012417259235381</v>
       </c>
       <c r="E69">
-        <v>-20.66243723789976</v>
+        <v>-21.99892124330951</v>
       </c>
       <c r="F69">
-        <v>-2.816072409597553</v>
+        <v>-2.155132969517078</v>
       </c>
       <c r="G69">
-        <v>-11.44399428718715</v>
+        <v>-11.22085358620366</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.958493992425696</v>
       </c>
       <c r="E70">
-        <v>-20.6658834066196</v>
+        <v>-22.24726275789015</v>
       </c>
       <c r="F70">
-        <v>-3.350274950519315</v>
+        <v>-1.631205497859641</v>
       </c>
       <c r="G70">
-        <v>-10.95261332333867</v>
+        <v>-10.59110506099579</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.894399474567519</v>
       </c>
       <c r="E71">
-        <v>-21.23610885366545</v>
+        <v>-23.00574592638288</v>
       </c>
       <c r="F71">
-        <v>-3.535917055691101</v>
+        <v>-2.683382862282323</v>
       </c>
       <c r="G71">
-        <v>-9.088686799999429</v>
+        <v>-11.67920523720683</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.829311779422957</v>
       </c>
       <c r="E72">
-        <v>-18.753268824058</v>
+        <v>-21.32265704890005</v>
       </c>
       <c r="F72">
-        <v>-3.407049595572388</v>
+        <v>-2.06974651437131</v>
       </c>
       <c r="G72">
-        <v>-11.04012428412376</v>
+        <v>-12.79248211224402</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.769877373936342</v>
       </c>
       <c r="E73">
-        <v>-21.67881700112931</v>
+        <v>-23.07468288620164</v>
       </c>
       <c r="F73">
-        <v>-3.319735529480305</v>
+        <v>-2.599972891759635</v>
       </c>
       <c r="G73">
-        <v>-12.52651619416451</v>
+        <v>-11.38557309005563</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.721389429425807</v>
       </c>
       <c r="E74">
-        <v>-21.57158273662768</v>
+        <v>-23.64046137177196</v>
       </c>
       <c r="F74">
-        <v>-3.228953917440105</v>
+        <v>-1.982540964408995</v>
       </c>
       <c r="G74">
-        <v>-11.10721580002263</v>
+        <v>-12.30040262328675</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.684929916046389</v>
       </c>
       <c r="E75">
-        <v>-21.71212392745573</v>
+        <v>-23.87806134600641</v>
       </c>
       <c r="F75">
-        <v>-3.236594778363528</v>
+        <v>-2.21713295614701</v>
       </c>
       <c r="G75">
-        <v>-11.02128728000531</v>
+        <v>-11.26442036550046</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.664851466069578</v>
       </c>
       <c r="E76">
-        <v>-21.13117958243372</v>
+        <v>-24.76811479831798</v>
       </c>
       <c r="F76">
-        <v>-3.2849068220296</v>
+        <v>-1.985846150346165</v>
       </c>
       <c r="G76">
-        <v>-11.03310592758051</v>
+        <v>-10.14088079929153</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.660747294212607</v>
       </c>
       <c r="E77">
-        <v>-20.92465399683991</v>
+        <v>-23.33151528954667</v>
       </c>
       <c r="F77">
-        <v>-3.755805526029424</v>
+        <v>-2.66703088975106</v>
       </c>
       <c r="G77">
-        <v>-10.55925430236247</v>
+        <v>-11.28563434131611</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.667546475515627</v>
       </c>
       <c r="E78">
-        <v>-22.53806777324072</v>
+        <v>-23.90549937001888</v>
       </c>
       <c r="F78">
-        <v>-3.842658191478147</v>
+        <v>-3.389957062583023</v>
       </c>
       <c r="G78">
-        <v>-10.29314272027923</v>
+        <v>-11.49933998751269</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.680033008503793</v>
       </c>
       <c r="E79">
-        <v>-21.88360365270418</v>
+        <v>-24.35953775944994</v>
       </c>
       <c r="F79">
-        <v>-3.696745415312028</v>
+        <v>-2.804949920480164</v>
       </c>
       <c r="G79">
-        <v>-11.11766057119903</v>
+        <v>-11.25406828959916</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.693796466372513</v>
       </c>
       <c r="E80">
-        <v>-21.9672717384699</v>
+        <v>-24.68758041656558</v>
       </c>
       <c r="F80">
-        <v>-4.371793608996984</v>
+        <v>-2.351933183604573</v>
       </c>
       <c r="G80">
-        <v>-11.23546964475954</v>
+        <v>-11.7083876961355</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.702985308767769</v>
       </c>
       <c r="E81">
-        <v>-23.48105002975395</v>
+        <v>-24.12935542564005</v>
       </c>
       <c r="F81">
-        <v>-3.263327851186673</v>
+        <v>-2.903394759363663</v>
       </c>
       <c r="G81">
-        <v>-10.52478490220757</v>
+        <v>-11.24731477669905</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.70156956869741</v>
       </c>
       <c r="E82">
-        <v>-24.08479524140457</v>
+        <v>-26.77351781329675</v>
       </c>
       <c r="F82">
-        <v>-3.416970951955717</v>
+        <v>-3.00927502405469</v>
       </c>
       <c r="G82">
-        <v>-9.808982056251898</v>
+        <v>-11.09997563692825</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.682674070779806</v>
       </c>
       <c r="E83">
-        <v>-23.03862717615257</v>
+        <v>-26.84176644506635</v>
       </c>
       <c r="F83">
-        <v>-3.823625622031425</v>
+        <v>-2.763983010574715</v>
       </c>
       <c r="G83">
-        <v>-10.82503814043731</v>
+        <v>-11.851022550695</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.64630076650047</v>
       </c>
       <c r="E84">
-        <v>-24.04458692069047</v>
+        <v>-26.23542188933532</v>
       </c>
       <c r="F84">
-        <v>-3.79311685058632</v>
+        <v>-3.48289491497271</v>
       </c>
       <c r="G84">
-        <v>-11.77847194520188</v>
+        <v>-10.28924951872505</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.590305876020095</v>
       </c>
       <c r="E85">
-        <v>-26.01056504095845</v>
+        <v>-25.5458394528693</v>
       </c>
       <c r="F85">
-        <v>-3.991992953385231</v>
+        <v>-2.734118708968987</v>
       </c>
       <c r="G85">
-        <v>-11.18797324790761</v>
+        <v>-12.45041337330775</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.511726503723869</v>
       </c>
       <c r="E86">
-        <v>-24.67289910383271</v>
+        <v>-28.57850868259206</v>
       </c>
       <c r="F86">
-        <v>-4.673887603654324</v>
+        <v>-3.454949112271866</v>
       </c>
       <c r="G86">
-        <v>-11.49707557436383</v>
+        <v>-10.26118602418865</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.4125870042824</v>
       </c>
       <c r="E87">
-        <v>-26.27401354482869</v>
+        <v>-29.47988105568581</v>
       </c>
       <c r="F87">
-        <v>-3.834730715433356</v>
+        <v>-3.854694369840824</v>
       </c>
       <c r="G87">
-        <v>-10.60117574052626</v>
+        <v>-11.31732619376356</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.296055716872777</v>
       </c>
       <c r="E88">
-        <v>-26.69048824236611</v>
+        <v>-30.18714265467777</v>
       </c>
       <c r="F88">
-        <v>-3.934322014802329</v>
+        <v>-3.258153868388788</v>
       </c>
       <c r="G88">
-        <v>-11.21302083545774</v>
+        <v>-10.31230746840607</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.165943874400119</v>
       </c>
       <c r="E89">
-        <v>-29.26020251733671</v>
+        <v>-29.20668048304006</v>
       </c>
       <c r="F89">
-        <v>-5.12063277092332</v>
+        <v>-3.808348042021594</v>
       </c>
       <c r="G89">
-        <v>-11.29607580194697</v>
+        <v>-10.3993748160889</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.025894075442221</v>
       </c>
       <c r="E90">
-        <v>-30.05083785128389</v>
+        <v>-31.06578435249002</v>
       </c>
       <c r="F90">
-        <v>-4.276856906064341</v>
+        <v>-3.656989578549471</v>
       </c>
       <c r="G90">
-        <v>-11.87738111427868</v>
+        <v>-11.31157908670738</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.880684251887499</v>
       </c>
       <c r="E91">
-        <v>-31.64233154925058</v>
+        <v>-31.7425942280174</v>
       </c>
       <c r="F91">
-        <v>-4.402000026340068</v>
+        <v>-3.342256354060216</v>
       </c>
       <c r="G91">
-        <v>-11.14531355808857</v>
+        <v>-12.0423489090461</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.738378715658018</v>
       </c>
       <c r="E92">
-        <v>-32.05528082977303</v>
+        <v>-33.71124867642392</v>
       </c>
       <c r="F92">
-        <v>-5.030706034042809</v>
+        <v>-3.433809176152423</v>
       </c>
       <c r="G92">
-        <v>-9.882933022508137</v>
+        <v>-12.2943873620419</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.60423928485713</v>
       </c>
       <c r="E93">
-        <v>-32.47930675771825</v>
+        <v>-33.82143097750455</v>
       </c>
       <c r="F93">
-        <v>-5.115787649984346</v>
+        <v>-4.257296666582037</v>
       </c>
       <c r="G93">
-        <v>-10.94963714289886</v>
+        <v>-11.317236809034</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.47958071338705</v>
       </c>
       <c r="E94">
-        <v>-35.09473371355928</v>
+        <v>-33.607976826679</v>
       </c>
       <c r="F94">
-        <v>-5.11023758838559</v>
+        <v>-3.984370316544669</v>
       </c>
       <c r="G94">
-        <v>-11.57507533781459</v>
+        <v>-11.28830264102077</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.369947551893244</v>
       </c>
       <c r="E95">
-        <v>-36.11286599622979</v>
+        <v>-37.70063276008816</v>
       </c>
       <c r="F95">
-        <v>-5.619665317024424</v>
+        <v>-4.332892647394116</v>
       </c>
       <c r="G95">
-        <v>-11.25172111281182</v>
+        <v>-10.75582125430223</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.278380634864337</v>
       </c>
       <c r="E96">
-        <v>-36.16298261807268</v>
+        <v>-40.25396754457302</v>
       </c>
       <c r="F96">
-        <v>-4.866807744827107</v>
+        <v>-5.197771171839413</v>
       </c>
       <c r="G96">
-        <v>-11.72270580559285</v>
+        <v>-12.31523386730269</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.206286358165736</v>
       </c>
       <c r="E97">
-        <v>-37.15100960554021</v>
+        <v>-40.4997300932063</v>
       </c>
       <c r="F97">
-        <v>-5.008882694816056</v>
+        <v>-4.528615983857972</v>
       </c>
       <c r="G97">
-        <v>-11.87168697595114</v>
+        <v>-11.47213392427096</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.154592941526947</v>
       </c>
       <c r="E98">
-        <v>-39.91420519672553</v>
+        <v>-42.75503468206134</v>
       </c>
       <c r="F98">
-        <v>-5.302833009536474</v>
+        <v>-4.649675252837898</v>
       </c>
       <c r="G98">
-        <v>-10.89939630379488</v>
+        <v>-11.26153688033576</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.123514908832139</v>
       </c>
       <c r="E99">
-        <v>-43.02253617016844</v>
+        <v>-41.59028626068148</v>
       </c>
       <c r="F99">
-        <v>-5.543193751867585</v>
+        <v>-5.503125620594172</v>
       </c>
       <c r="G99">
-        <v>-11.33356110908814</v>
+        <v>-12.81109730981134</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.117524699055207</v>
       </c>
       <c r="E100">
-        <v>-44.69409102435372</v>
+        <v>-46.30332501924546</v>
       </c>
       <c r="F100">
-        <v>-5.562425957858381</v>
+        <v>-6.274710094666577</v>
       </c>
       <c r="G100">
-        <v>-12.43079176989649</v>
+        <v>-11.35704280859819</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.131851087649939</v>
       </c>
       <c r="E101">
-        <v>-45.1028559948931</v>
+        <v>-48.11966650864099</v>
       </c>
       <c r="F101">
-        <v>-5.801069494563488</v>
+        <v>-6.455401876239234</v>
       </c>
       <c r="G101">
-        <v>-12.26415214963173</v>
+        <v>-13.408246893094</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.17110515866173</v>
       </c>
       <c r="E102">
-        <v>-47.5269820947541</v>
+        <v>-49.14884713577172</v>
       </c>
       <c r="F102">
-        <v>-6.182254352105319</v>
+        <v>-6.209622782726412</v>
       </c>
       <c r="G102">
-        <v>-13.36179662863249</v>
+        <v>-12.42659068760715</v>
       </c>
     </row>
   </sheetData>
